--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-12-2025.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Read timed out. (read timeout=30)</t>
+          <t>£9.92</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>£9.60</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£11.10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Read timed out.</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Read timed out. (read timeout=30)</t>
+          <t>£39.50</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>£37.14</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Read timed out.</t>
+          <t>£38.50</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>£78.85</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>£39.6</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>£634.53</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>£68.31</t>
+          <t>Error: HTTPSConnectionPool(host='www.planetinsulation.co.uk', port=443): Max retries exceeded with url: /products/celotex-pl4000-insulation-boards (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
